--- a/BTS_SIO_2025-Annexe_8-1-Epreuve_E5-Tableau_de_synthèse-Complété.xlsx
+++ b/BTS_SIO_2025-Annexe_8-1-Epreuve_E5-Tableau_de_synthèse-Complété.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ITLP\Documents\GitHub\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F66D9F7-57FB-4A88-B9D2-0CBE91818991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A8B6273-C3D7-428F-9002-9CB2E4CDF79B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="54">
   <si>
     <t>Gérer le patrimoine informatique</t>
   </si>
@@ -186,6 +186,24 @@
   </si>
   <si>
     <t>Réalisations en milieu professionnel en cours de seconde année au sein de  du 04/01/2027 au 05/02/2027</t>
+  </si>
+  <si>
+    <t>TP_DHCP_ROUTEUR_VLAN</t>
+  </si>
+  <si>
+    <t>07/09/2026 au 21/09/2026</t>
+  </si>
+  <si>
+    <t>Projet PROXMOX</t>
+  </si>
+  <si>
+    <t>11/09/2026 au ?/?/202?</t>
+  </si>
+  <si>
+    <t>Projet ARENA</t>
+  </si>
+  <si>
+    <t>08/09/2026 au ?/?/202?</t>
   </si>
 </sst>
 </file>
@@ -711,9 +729,54 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -737,51 +800,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1173,56 +1191,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="19"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:43" ht="41.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="26" t="s">
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="21"/>
-      <c r="H3" s="27"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="42"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="25"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="40"/>
       <c r="F4" s="14" t="s">
         <v>8</v>
       </c>
@@ -1234,22 +1252,22 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="40"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="34"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="30" t="s">
         <v>20</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1272,8 +1290,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="325" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="29"/>
-      <c r="B7" s="37"/>
+      <c r="A7" s="22"/>
+      <c r="B7" s="31"/>
       <c r="C7" s="17" t="s">
         <v>9</v>
       </c>
@@ -1329,16 +1347,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="32"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="26"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1379,7 +1397,7 @@
       <c r="A9" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="41"/>
+      <c r="B9" s="19"/>
       <c r="C9" s="18"/>
       <c r="D9" s="18" t="s">
         <v>26</v>
@@ -1430,7 +1448,7 @@
       <c r="A10" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="41"/>
+      <c r="B10" s="19"/>
       <c r="C10" s="18"/>
       <c r="D10" s="18"/>
       <c r="E10" s="18"/>
@@ -1479,7 +1497,7 @@
       <c r="A11" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="41" t="s">
+      <c r="B11" s="19" t="s">
         <v>40</v>
       </c>
       <c r="C11" s="18" t="s">
@@ -1536,7 +1554,7 @@
       <c r="A12" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="41" t="s">
+      <c r="B12" s="19" t="s">
         <v>44</v>
       </c>
       <c r="C12" s="18"/>
@@ -1584,13 +1602,21 @@
       <c r="AQ12"/>
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="11"/>
-      <c r="B13" s="41"/>
-      <c r="C13" s="18"/>
+      <c r="A13" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>26</v>
+      </c>
       <c r="D13" s="18"/>
       <c r="E13" s="18"/>
       <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
+      <c r="G13" s="18" t="s">
+        <v>26</v>
+      </c>
       <c r="H13" s="18"/>
       <c r="I13"/>
       <c r="J13"/>
@@ -1629,13 +1655,23 @@
       <c r="AQ13"/>
     </row>
     <row r="14" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="11"/>
-      <c r="B14" s="41"/>
-      <c r="C14" s="18"/>
+      <c r="A14" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>26</v>
+      </c>
       <c r="D14" s="18"/>
       <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
+      <c r="F14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>26</v>
+      </c>
       <c r="H14" s="18"/>
       <c r="I14"/>
       <c r="J14"/>
@@ -1674,13 +1710,23 @@
       <c r="AQ14"/>
     </row>
     <row r="15" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="11"/>
-      <c r="B15" s="41"/>
-      <c r="C15" s="18"/>
+      <c r="A15" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>26</v>
+      </c>
       <c r="D15" s="18"/>
       <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
+      <c r="F15" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="18" t="s">
+        <v>26</v>
+      </c>
       <c r="H15" s="18"/>
       <c r="I15"/>
       <c r="J15"/>
@@ -1720,7 +1766,7 @@
     </row>
     <row r="16" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11"/>
-      <c r="B16" s="41"/>
+      <c r="B16" s="19"/>
       <c r="C16" s="18"/>
       <c r="D16" s="18"/>
       <c r="E16" s="18"/>
@@ -1765,7 +1811,7 @@
     </row>
     <row r="17" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11"/>
-      <c r="B17" s="41"/>
+      <c r="B17" s="19"/>
       <c r="C17" s="18"/>
       <c r="D17" s="18"/>
       <c r="E17" s="18"/>
@@ -1809,8 +1855,8 @@
       <c r="AQ17"/>
     </row>
     <row r="18" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="42"/>
-      <c r="B18" s="41"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="19"/>
       <c r="C18" s="18"/>
       <c r="D18" s="18"/>
       <c r="E18" s="18"/>
@@ -1854,16 +1900,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A19" s="33" t="s">
+      <c r="A19" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="34"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="35"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="29"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1904,7 +1950,7 @@
       <c r="A20" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="41" t="s">
+      <c r="B20" s="19" t="s">
         <v>31</v>
       </c>
       <c r="C20" s="18" t="s">
@@ -1955,7 +2001,7 @@
       <c r="A21" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="41" t="s">
+      <c r="B21" s="19" t="s">
         <v>33</v>
       </c>
       <c r="C21" s="18" t="s">
@@ -2008,7 +2054,7 @@
       <c r="A22" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="41" t="s">
+      <c r="B22" s="19" t="s">
         <v>34</v>
       </c>
       <c r="C22" s="18"/>
@@ -2061,7 +2107,7 @@
       <c r="A23" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="41" t="s">
+      <c r="B23" s="19" t="s">
         <v>35</v>
       </c>
       <c r="C23" s="18"/>
@@ -2114,7 +2160,7 @@
       <c r="A24" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="41" t="s">
+      <c r="B24" s="19" t="s">
         <v>36</v>
       </c>
       <c r="C24" s="18" t="s">
@@ -2167,7 +2213,7 @@
       <c r="A25" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="41" t="s">
+      <c r="B25" s="19" t="s">
         <v>37</v>
       </c>
       <c r="C25" s="18" t="s">
@@ -2220,7 +2266,7 @@
       <c r="A26" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="41" t="s">
+      <c r="B26" s="19" t="s">
         <v>38</v>
       </c>
       <c r="C26" s="18"/>
@@ -2268,16 +2314,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A27" s="33" t="s">
+      <c r="A27" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="B27" s="34"/>
-      <c r="C27" s="34"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="35"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="29"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2722,6 +2768,11 @@
     <row r="81" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2729,11 +2780,6 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
